--- a/artfynd/A 69023-2021 artfynd.xlsx
+++ b/artfynd/A 69023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118328523</v>
+        <v>118328526</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567824</v>
+        <v>567810</v>
       </c>
       <c r="R2" t="n">
-        <v>7200541</v>
+        <v>7200714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118328526</v>
+        <v>118328523</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567810</v>
+        <v>567824</v>
       </c>
       <c r="R3" t="n">
-        <v>7200714</v>
+        <v>7200541</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 69023-2021 artfynd.xlsx
+++ b/artfynd/A 69023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118328526</v>
+        <v>118328523</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567810</v>
+        <v>567824</v>
       </c>
       <c r="R2" t="n">
-        <v>7200714</v>
+        <v>7200541</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118328523</v>
+        <v>118328526</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567824</v>
+        <v>567810</v>
       </c>
       <c r="R3" t="n">
-        <v>7200541</v>
+        <v>7200714</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 69023-2021 artfynd.xlsx
+++ b/artfynd/A 69023-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118328523</v>
+        <v>118328521</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1561</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Urnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tholurna dissimilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) Norman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567824</v>
+        <v>567555</v>
       </c>
       <c r="R2" t="n">
-        <v>7200541</v>
+        <v>7200452</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118328526</v>
+        <v>118328522</v>
       </c>
       <c r="B3" t="n">
-        <v>79572</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1561</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Urnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tholurna dissimilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) Norman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567810</v>
+        <v>567560</v>
       </c>
       <c r="R3" t="n">
-        <v>7200714</v>
+        <v>7200459</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +886,220 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118328523</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalakullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567824</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7200541</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118328526</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalakullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567810</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7200714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
